--- a/mmm_104_weeks_dataset.xlsx
+++ b/mmm_104_weeks_dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\MMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{060F7A04-ACB7-4F04-A210-7A4F9DBF93DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FE29FC-AD74-4F9C-A1D9-FA605BD20D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MMM_Data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="533">
   <si>
     <t>Week</t>
   </si>
@@ -1534,6 +1534,93 @@
   </si>
   <si>
     <t>0.6-0.7</t>
+  </si>
+  <si>
+    <t>revenue/spend</t>
+  </si>
+  <si>
+    <t>revenue = volume * price</t>
+  </si>
+  <si>
+    <t>2.3 = volume * price / spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coeff * X = volume </t>
+  </si>
+  <si>
+    <t xml:space="preserve">media </t>
+  </si>
+  <si>
+    <t>non - media</t>
+  </si>
+  <si>
+    <t>youtube</t>
+  </si>
+  <si>
+    <t>meta</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>200K</t>
+  </si>
+  <si>
+    <t>2K</t>
+  </si>
+  <si>
+    <t>3K</t>
+  </si>
+  <si>
+    <t>300K</t>
+  </si>
+  <si>
+    <t>4K</t>
+  </si>
+  <si>
+    <t>X - mean/ std</t>
+  </si>
+  <si>
+    <t>volume = X * coeff</t>
+  </si>
+  <si>
+    <t>coeff = volume/X</t>
+  </si>
+  <si>
+    <t>Y_coeff = 100</t>
+  </si>
+  <si>
+    <t>meta_coeff = 200</t>
+  </si>
+  <si>
+    <t>Ridge = it's regression with mean =0  , std = 1</t>
+  </si>
+  <si>
+    <t>lasso = regression with laplace priors</t>
+  </si>
+  <si>
+    <t>(x_pred - x_actual)^2</t>
+  </si>
+  <si>
+    <t>(x_pred - x_actual)^2 + (coeff_model - coeff_prior)^2</t>
+  </si>
+  <si>
+    <t>(2,3)</t>
+  </si>
+  <si>
+    <t>(4,5)</t>
+  </si>
+  <si>
+    <t>ridege for regularization</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>optimizers</t>
+  </si>
+  <si>
+    <t>LBFGS</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1590,6 +1677,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6069,11 +6158,11 @@
         <v>0.33548387096774196</v>
       </c>
       <c r="T3" s="4">
-        <f>R3+$S$2*T2</f>
+        <f t="shared" ref="T3:T34" si="1">R3+$S$2*T2</f>
         <v>0.58322580645161293</v>
       </c>
       <c r="W3">
-        <f t="shared" ref="W3:W66" si="1" xml:space="preserve"> (T3^$U$2) / (T3^$U$2 + $V$2^$U$2)</f>
+        <f t="shared" ref="W3:W66" si="2" xml:space="preserve"> (T3^$U$2) / (T3^$U$2 + $V$2^$U$2)</f>
         <v>0.22577422577422579</v>
       </c>
     </row>
@@ -6089,11 +6178,11 @@
         <v>0.32258064516129031</v>
       </c>
       <c r="T4" s="4">
-        <f>R4+$S$2*T3</f>
+        <f t="shared" si="1"/>
         <v>0.78916129032258064</v>
       </c>
       <c r="W4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28293856402664691</v>
       </c>
     </row>
@@ -6106,11 +6195,11 @@
         <v>0.36129032258064514</v>
       </c>
       <c r="T5" s="4">
-        <f>R5+$S$2*T4</f>
+        <f t="shared" si="1"/>
         <v>0.99261935483870967</v>
       </c>
       <c r="W5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.3316891449070401</v>
       </c>
     </row>
@@ -6123,11 +6212,11 @@
         <v>0.38709677419354838</v>
       </c>
       <c r="T6" s="4">
-        <f>R6+$S$2*T5</f>
+        <f t="shared" si="1"/>
         <v>1.1811922580645162</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.37130489522289067</v>
       </c>
     </row>
@@ -6140,11 +6229,11 @@
         <v>0.41290322580645161</v>
       </c>
       <c r="T7" s="4">
-        <f>R7+$S$2*T6</f>
+        <f t="shared" si="1"/>
         <v>1.3578570322580645</v>
       </c>
       <c r="W7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.40438202675500562</v>
       </c>
     </row>
@@ -6157,11 +6246,11 @@
         <v>0.4</v>
       </c>
       <c r="T8" s="4">
-        <f>R8+$S$2*T7</f>
+        <f t="shared" si="1"/>
         <v>1.4862856258064516</v>
       </c>
       <c r="W8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.42632353895634767</v>
       </c>
     </row>
@@ -6174,11 +6263,11 @@
         <v>0.43870967741935485</v>
       </c>
       <c r="T9" s="4">
-        <f>R9+$S$2*T8</f>
+        <f t="shared" si="1"/>
         <v>1.6277381780645162</v>
       </c>
       <c r="W9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.44869229756072226</v>
       </c>
     </row>
@@ -6191,11 +6280,11 @@
         <v>0.46451612903225808</v>
       </c>
       <c r="T10" s="4">
-        <f>R10+$S$2*T9</f>
+        <f t="shared" si="1"/>
         <v>1.7667066714838711</v>
       </c>
       <c r="W10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.46903218794785728</v>
       </c>
     </row>
@@ -6208,11 +6297,11 @@
         <v>0.45161290322580644</v>
       </c>
       <c r="T11" s="4">
-        <f>R11+$S$2*T10</f>
+        <f t="shared" si="1"/>
         <v>1.8649782404129034</v>
       </c>
       <c r="W11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.48253266238664877</v>
       </c>
     </row>
@@ -6225,11 +6314,11 @@
         <v>0.4258064516129032</v>
       </c>
       <c r="T12" s="4">
-        <f>R12+$S$2*T11</f>
+        <f t="shared" si="1"/>
         <v>1.9177890439432259</v>
       </c>
       <c r="W12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.48950799096956615</v>
       </c>
     </row>
@@ -6242,11 +6331,11 @@
         <v>0.47741935483870968</v>
       </c>
       <c r="T13" s="4">
-        <f>R13+$S$2*T12</f>
+        <f t="shared" si="1"/>
         <v>2.0116505899932906</v>
       </c>
       <c r="W13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.50145209431030102</v>
       </c>
     </row>
@@ -6259,11 +6348,11 @@
         <v>0.49032258064516127</v>
       </c>
       <c r="T14" s="4">
-        <f>R14+$S$2*T13</f>
+        <f t="shared" si="1"/>
         <v>2.0996430526397938</v>
       </c>
       <c r="W14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.51215264979906405</v>
       </c>
     </row>
@@ -6276,11 +6365,11 @@
         <v>0.5161290322580645</v>
       </c>
       <c r="T15" s="4">
-        <f>R15+$S$2*T14</f>
+        <f t="shared" si="1"/>
         <v>2.1958434743698998</v>
       </c>
       <c r="W15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.52333779555483895</v>
       </c>
     </row>
@@ -6293,11 +6382,11 @@
         <v>0.50322580645161286</v>
       </c>
       <c r="T16" s="4">
-        <f>R16+$S$2*T15</f>
+        <f t="shared" si="1"/>
         <v>2.2599005859475327</v>
       </c>
       <c r="W16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.53050547550392224</v>
       </c>
     </row>
@@ -6310,11 +6399,11 @@
         <v>0.54193548387096779</v>
       </c>
       <c r="T17" s="4">
-        <f>R17+$S$2*T16</f>
+        <f t="shared" si="1"/>
         <v>2.3498559526289942</v>
       </c>
       <c r="W17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.54021465957022619</v>
       </c>
     </row>
@@ -6327,11 +6416,11 @@
         <v>0.56774193548387097</v>
       </c>
       <c r="T18" s="4">
-        <f>R18+$S$2*T17</f>
+        <f t="shared" si="1"/>
         <v>2.4476266975870664</v>
       </c>
       <c r="W18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.55032197259607163</v>
       </c>
     </row>
@@ -6344,11 +6433,11 @@
         <v>0.55483870967741933</v>
       </c>
       <c r="T19" s="4">
-        <f>R19+$S$2*T18</f>
+        <f t="shared" si="1"/>
         <v>2.5129400677470723</v>
       </c>
       <c r="W19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.55682992240612006</v>
       </c>
     </row>
@@ -6361,11 +6450,11 @@
         <v>0.52903225806451615</v>
       </c>
       <c r="T20" s="4">
-        <f>R20+$S$2*T19</f>
+        <f t="shared" si="1"/>
         <v>2.5393843122621744</v>
       </c>
       <c r="W20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.55941161566835651</v>
       </c>
     </row>
@@ -6378,11 +6467,11 @@
         <v>0.58064516129032262</v>
       </c>
       <c r="T21" s="4">
-        <f>R21+$S$2*T20</f>
+        <f t="shared" si="1"/>
         <v>2.6121526111000621</v>
       </c>
       <c r="W21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.56636300473089241</v>
       </c>
     </row>
@@ -6395,11 +6484,11 @@
         <v>0.59354838709677415</v>
       </c>
       <c r="T22" s="4">
-        <f>R22+$S$2*T21</f>
+        <f t="shared" si="1"/>
         <v>2.6832704759768236</v>
       </c>
       <c r="W22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.57294800497661935</v>
       </c>
     </row>
@@ -6412,11 +6501,11 @@
         <v>0.61935483870967745</v>
       </c>
       <c r="T23" s="4">
-        <f>R23+$S$2*T22</f>
+        <f t="shared" si="1"/>
         <v>2.7659712194911368</v>
       </c>
       <c r="W23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.58035835553922199</v>
       </c>
     </row>
@@ -6429,11 +6518,11 @@
         <v>0.6064516129032258</v>
       </c>
       <c r="T24" s="4">
-        <f>R24+$S$2*T23</f>
+        <f t="shared" si="1"/>
         <v>2.8192285884961352</v>
       </c>
       <c r="W24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.58499582178480769</v>
       </c>
     </row>
@@ -6446,11 +6535,11 @@
         <v>0.64516129032258063</v>
       </c>
       <c r="T25" s="4">
-        <f>R25+$S$2*T24</f>
+        <f t="shared" si="1"/>
         <v>2.9005441611194889</v>
       </c>
       <c r="W25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5918820575339705</v>
       </c>
     </row>
@@ -6463,11 +6552,11 @@
         <v>0.67096774193548392</v>
       </c>
       <c r="T26" s="4">
-        <f>R26+$S$2*T25</f>
+        <f t="shared" si="1"/>
         <v>2.9914030708310748</v>
       </c>
       <c r="W26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.59931106111472632</v>
       </c>
     </row>
@@ -6480,11 +6569,11 @@
         <v>0.65806451612903227</v>
       </c>
       <c r="T27" s="4">
-        <f>R27+$S$2*T26</f>
+        <f t="shared" si="1"/>
         <v>3.0511869727938925</v>
       </c>
       <c r="W27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.60405346094449397</v>
       </c>
     </row>
@@ -6497,11 +6586,11 @@
         <v>0.63225806451612898</v>
       </c>
       <c r="T28" s="4">
-        <f>R28+$S$2*T27</f>
+        <f t="shared" si="1"/>
         <v>3.0732076427512434</v>
       </c>
       <c r="W28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.60577209906681784</v>
       </c>
     </row>
@@ -6514,11 +6603,11 @@
         <v>0.68387096774193545</v>
       </c>
       <c r="T29" s="4">
-        <f>R29+$S$2*T28</f>
+        <f t="shared" si="1"/>
         <v>3.1424370819429299</v>
       </c>
       <c r="W29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.61107934465104741</v>
       </c>
     </row>
@@ -6531,11 +6620,11 @@
         <v>0.6967741935483871</v>
       </c>
       <c r="T30" s="4">
-        <f>R30+$S$2*T29</f>
+        <f t="shared" si="1"/>
         <v>3.2107238591027314</v>
       </c>
       <c r="W30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.61617616782625029</v>
       </c>
     </row>
@@ -6548,11 +6637,11 @@
         <v>0.72258064516129028</v>
       </c>
       <c r="T31" s="4">
-        <f>R31+$S$2*T30</f>
+        <f t="shared" si="1"/>
         <v>3.2911597324434756</v>
       </c>
       <c r="W31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.62201103328317153</v>
       </c>
     </row>
@@ -6565,11 +6654,11 @@
         <v>0.70967741935483875</v>
       </c>
       <c r="T32" s="4">
-        <f>R32+$S$2*T31</f>
+        <f t="shared" si="1"/>
         <v>3.3426052053096198</v>
       </c>
       <c r="W32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.62565079710319071</v>
       </c>
     </row>
@@ -6582,11 +6671,11 @@
         <v>0.74838709677419357</v>
       </c>
       <c r="T33" s="4">
-        <f>R33+$S$2*T32</f>
+        <f t="shared" si="1"/>
         <v>3.4224712610218897</v>
       </c>
       <c r="W33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.63116448133593406</v>
       </c>
     </row>
@@ -6599,11 +6688,11 @@
         <v>0.77419354838709675</v>
       </c>
       <c r="T34" s="4">
-        <f>R34+$S$2*T33</f>
+        <f t="shared" si="1"/>
         <v>3.5121705572046089</v>
       </c>
       <c r="W34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.63716652464863832</v>
       </c>
     </row>
@@ -6616,11 +6705,11 @@
         <v>0.76129032258064511</v>
       </c>
       <c r="T35" s="4">
-        <f>R35+$S$2*T34</f>
+        <f t="shared" ref="T35:T66" si="3">R35+$S$2*T34</f>
         <v>3.5710267683443324</v>
       </c>
       <c r="W35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.64099975046531954</v>
       </c>
     </row>
@@ -6633,11 +6722,11 @@
         <v>0.73548387096774193</v>
       </c>
       <c r="T36" s="4">
-        <f>R36+$S$2*T35</f>
+        <f t="shared" si="3"/>
         <v>3.5923052856432078</v>
       </c>
       <c r="W36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.64236573329884528</v>
       </c>
     </row>
@@ -6650,11 +6739,11 @@
         <v>0.7870967741935484</v>
       </c>
       <c r="T37" s="4">
-        <f>R37+$S$2*T36</f>
+        <f t="shared" si="3"/>
         <v>3.6609410027081148</v>
       </c>
       <c r="W37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.64670184708810285</v>
       </c>
     </row>
@@ -6667,11 +6756,11 @@
         <v>0.8</v>
       </c>
       <c r="T38" s="4">
-        <f>R38+$S$2*T37</f>
+        <f t="shared" si="3"/>
         <v>3.7287528021664924</v>
       </c>
       <c r="W38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.65088387139978487</v>
       </c>
     </row>
@@ -6684,11 +6773,11 @@
         <v>0.82580645161290323</v>
       </c>
       <c r="T39" s="4">
-        <f>R39+$S$2*T38</f>
+        <f t="shared" si="3"/>
         <v>3.8088086933460974</v>
       </c>
       <c r="W39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.65569532315791879</v>
       </c>
     </row>
@@ -6701,11 +6790,11 @@
         <v>0.81290322580645158</v>
       </c>
       <c r="T40" s="4">
-        <f>R40+$S$2*T39</f>
+        <f t="shared" si="3"/>
         <v>3.8599501804833296</v>
       </c>
       <c r="W40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.65870017006952786</v>
       </c>
     </row>
@@ -6718,11 +6807,11 @@
         <v>0.85161290322580641</v>
       </c>
       <c r="T41" s="4">
-        <f>R41+$S$2*T40</f>
+        <f t="shared" si="3"/>
         <v>3.9395730476124702</v>
       </c>
       <c r="W41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.6632754603794393</v>
       </c>
     </row>
@@ -6735,11 +6824,11 @@
         <v>0.8774193548387097</v>
       </c>
       <c r="T42" s="4">
-        <f>R42+$S$2*T41</f>
+        <f t="shared" si="3"/>
         <v>4.0290777929286854</v>
       </c>
       <c r="W42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.66827430849445391</v>
       </c>
     </row>
@@ -6752,11 +6841,11 @@
         <v>0.86451612903225805</v>
       </c>
       <c r="T43" s="4">
-        <f>R43+$S$2*T42</f>
+        <f t="shared" si="3"/>
         <v>4.0877783633752065</v>
       </c>
       <c r="W43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.67147292811574155</v>
       </c>
     </row>
@@ -6769,11 +6858,11 @@
         <v>0.83870967741935487</v>
       </c>
       <c r="T44" s="4">
-        <f>R44+$S$2*T43</f>
+        <f t="shared" si="3"/>
         <v>4.10893236811952</v>
       </c>
       <c r="W44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.67261055132361047</v>
       </c>
     </row>
@@ -6786,11 +6875,11 @@
         <v>0.89032258064516134</v>
       </c>
       <c r="T45" s="4">
-        <f>R45+$S$2*T44</f>
+        <f t="shared" si="3"/>
         <v>4.1774684751407776</v>
       </c>
       <c r="W45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.67624278326172726</v>
       </c>
     </row>
@@ -6803,11 +6892,11 @@
         <v>0.90322580645161288</v>
       </c>
       <c r="T46" s="4">
-        <f>R46+$S$2*T45</f>
+        <f t="shared" si="3"/>
         <v>4.245200586564235</v>
       </c>
       <c r="W46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.67975408118952196</v>
       </c>
     </row>
@@ -6820,11 +6909,11 @@
         <v>0.92903225806451617</v>
       </c>
       <c r="T47" s="4">
-        <f>R47+$S$2*T46</f>
+        <f t="shared" si="3"/>
         <v>4.3251927273159039</v>
       </c>
       <c r="W47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.68380410112045709</v>
       </c>
     </row>
@@ -6837,11 +6926,11 @@
         <v>0.91612903225806452</v>
       </c>
       <c r="T48" s="4">
-        <f>R48+$S$2*T47</f>
+        <f t="shared" si="3"/>
         <v>4.3762832141107877</v>
       </c>
       <c r="W48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.68633764642480477</v>
       </c>
     </row>
@@ -6854,11 +6943,11 @@
         <v>0.95483870967741935</v>
       </c>
       <c r="T49" s="4">
-        <f>R49+$S$2*T48</f>
+        <f t="shared" si="3"/>
         <v>4.4558652809660497</v>
       </c>
       <c r="W49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.69020419216357598</v>
       </c>
     </row>
@@ -6871,11 +6960,11 @@
         <v>0.98064516129032253</v>
       </c>
       <c r="T50" s="4">
-        <f>R50+$S$2*T49</f>
+        <f t="shared" si="3"/>
         <v>4.5453373860631627</v>
       </c>
       <c r="W50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.69443897510026686</v>
       </c>
     </row>
@@ -6888,11 +6977,11 @@
         <v>0.967741935483871</v>
       </c>
       <c r="T51" s="4">
-        <f>R51+$S$2*T50</f>
+        <f t="shared" si="3"/>
         <v>4.6040118443344014</v>
       </c>
       <c r="W51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.69715378361778602</v>
       </c>
     </row>
@@ -6905,11 +6994,11 @@
         <v>0.9419354838709677</v>
       </c>
       <c r="T52" s="4">
-        <f>R52+$S$2*T51</f>
+        <f t="shared" si="3"/>
         <v>4.6251449593384883</v>
       </c>
       <c r="W52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.69811981288335501</v>
       </c>
     </row>
@@ -6922,11 +7011,11 @@
         <v>0.99354838709677418</v>
       </c>
       <c r="T53" s="4">
-        <f>R53+$S$2*T52</f>
+        <f t="shared" si="3"/>
         <v>4.6936643545675647</v>
       </c>
       <c r="W53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.70120999589182309</v>
       </c>
     </row>
@@ -6939,11 +7028,11 @@
         <v>1.0064516129032257</v>
       </c>
       <c r="T54" s="4">
-        <f>R54+$S$2*T53</f>
+        <f t="shared" si="3"/>
         <v>4.7613830965572781</v>
       </c>
       <c r="W54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.70420253202065297</v>
       </c>
     </row>
@@ -6956,11 +7045,11 @@
         <v>1.032258064516129</v>
       </c>
       <c r="T55" s="4">
-        <f>R55+$S$2*T54</f>
+        <f t="shared" si="3"/>
         <v>4.8413645417619513</v>
       </c>
       <c r="W55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.70766065924548549</v>
       </c>
     </row>
@@ -6973,11 +7062,11 @@
         <v>1.0193548387096774</v>
       </c>
       <c r="T56" s="4">
-        <f>R56+$S$2*T55</f>
+        <f t="shared" si="3"/>
         <v>4.8924464721192384</v>
       </c>
       <c r="W56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.70982727133388168</v>
       </c>
     </row>
@@ -6990,11 +7079,11 @@
         <v>1.0580645161290323</v>
       </c>
       <c r="T57" s="4">
-        <f>R57+$S$2*T56</f>
+        <f t="shared" si="3"/>
         <v>4.9720216938244235</v>
       </c>
       <c r="W57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.71313915994100663</v>
       </c>
     </row>
@@ -7007,11 +7096,11 @@
         <v>1.0838709677419356</v>
       </c>
       <c r="T58" s="4">
-        <f>R58+$S$2*T57</f>
+        <f t="shared" si="3"/>
         <v>5.0614883228014751</v>
       </c>
       <c r="W58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.71677358814826331</v>
       </c>
     </row>
@@ -7024,11 +7113,11 @@
         <v>1.0709677419354839</v>
       </c>
       <c r="T59" s="4">
-        <f>R59+$S$2*T58</f>
+        <f t="shared" si="3"/>
         <v>5.1201584001766642</v>
       </c>
       <c r="W59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.71910737267440905</v>
       </c>
     </row>
@@ -7041,11 +7130,11 @@
         <v>1.0451612903225806</v>
       </c>
       <c r="T60" s="4">
-        <f>R60+$S$2*T59</f>
+        <f t="shared" si="3"/>
         <v>5.1412880104639118</v>
       </c>
       <c r="W60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.71993847649479181</v>
       </c>
     </row>
@@ -7058,11 +7147,11 @@
         <v>1.096774193548387</v>
       </c>
       <c r="T61" s="4">
-        <f>R61+$S$2*T60</f>
+        <f t="shared" si="3"/>
         <v>5.209804601919517</v>
       </c>
       <c r="W61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.72259997178459923</v>
       </c>
     </row>
@@ -7075,11 +7164,11 @@
         <v>1.1096774193548387</v>
       </c>
       <c r="T62" s="4">
-        <f>R62+$S$2*T61</f>
+        <f t="shared" si="3"/>
         <v>5.2775211008904526</v>
       </c>
       <c r="W62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.72518114722397897</v>
       </c>
     </row>
@@ -7092,11 +7181,11 @@
         <v>1.1354838709677419</v>
       </c>
       <c r="T63" s="4">
-        <f>R63+$S$2*T62</f>
+        <f t="shared" si="3"/>
         <v>5.3575007516801048</v>
       </c>
       <c r="W63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.72816856327968504</v>
       </c>
     </row>
@@ -7109,11 +7198,11 @@
         <v>1.1225806451612903</v>
       </c>
       <c r="T64" s="4">
-        <f>R64+$S$2*T63</f>
+        <f t="shared" si="3"/>
         <v>5.4085812465053742</v>
       </c>
       <c r="W64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.73004277965590247</v>
       </c>
     </row>
@@ -7126,11 +7215,11 @@
         <v>1.1612903225806452</v>
       </c>
       <c r="T65" s="4">
-        <f>R65+$S$2*T64</f>
+        <f t="shared" si="3"/>
         <v>5.4881553197849442</v>
       </c>
       <c r="W65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.73291152298675355</v>
       </c>
     </row>
@@ -7143,11 +7232,11 @@
         <v>1.1870967741935483</v>
       </c>
       <c r="T66" s="4">
-        <f>R66+$S$2*T65</f>
+        <f t="shared" si="3"/>
         <v>5.5776210300215041</v>
       </c>
       <c r="W66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.73606492168501536</v>
       </c>
     </row>
@@ -7156,15 +7245,15 @@
         <v>455</v>
       </c>
       <c r="R67" s="2">
-        <f t="shared" ref="R67:R105" si="2">Q67/$P$2</f>
+        <f t="shared" ref="R67:R105" si="4">Q67/$P$2</f>
         <v>1.1741935483870967</v>
       </c>
       <c r="T67" s="4">
-        <f>R67+$S$2*T66</f>
+        <f t="shared" ref="T67:T98" si="5">R67+$S$2*T66</f>
         <v>5.6362903724043001</v>
       </c>
       <c r="W67">
-        <f t="shared" ref="W67:W105" si="3" xml:space="preserve"> (T67^$U$2) / (T67^$U$2 + $V$2^$U$2)</f>
+        <f t="shared" ref="W67:W105" si="6" xml:space="preserve"> (T67^$U$2) / (T67^$U$2 + $V$2^$U$2)</f>
         <v>0.73809272533329606</v>
       </c>
     </row>
@@ -7173,15 +7262,15 @@
         <v>445</v>
       </c>
       <c r="R68" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1483870967741936</v>
       </c>
       <c r="T68" s="4">
-        <f>R68+$S$2*T67</f>
+        <f t="shared" si="5"/>
         <v>5.6574193946976337</v>
       </c>
       <c r="W68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.73881540282553981</v>
       </c>
     </row>
@@ -7190,15 +7279,15 @@
         <v>465</v>
       </c>
       <c r="R69" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2</v>
       </c>
       <c r="T69" s="4">
-        <f>R69+$S$2*T68</f>
+        <f t="shared" si="5"/>
         <v>5.7259355157581071</v>
       </c>
       <c r="W69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.74113167319080964</v>
       </c>
     </row>
@@ -7207,15 +7296,15 @@
         <v>470</v>
       </c>
       <c r="R70" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2129032258064516</v>
       </c>
       <c r="T70" s="4">
-        <f>R70+$S$2*T69</f>
+        <f t="shared" si="5"/>
         <v>5.7936516384129373</v>
       </c>
       <c r="W70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.74338088321236917</v>
       </c>
     </row>
@@ -7224,15 +7313,15 @@
         <v>480</v>
       </c>
       <c r="R71" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2387096774193549</v>
       </c>
       <c r="T71" s="4">
-        <f>R71+$S$2*T70</f>
+        <f t="shared" si="5"/>
         <v>5.8736309881497046</v>
       </c>
       <c r="W71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.74598758780921759</v>
       </c>
     </row>
@@ -7241,15 +7330,15 @@
         <v>475</v>
       </c>
       <c r="R72" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2258064516129032</v>
       </c>
       <c r="T72" s="4">
-        <f>R72+$S$2*T71</f>
+        <f t="shared" si="5"/>
         <v>5.9247112421326671</v>
       </c>
       <c r="W72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.74762487377877407</v>
       </c>
     </row>
@@ -7258,15 +7347,15 @@
         <v>490</v>
       </c>
       <c r="R73" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.264516129032258</v>
       </c>
       <c r="T73" s="4">
-        <f>R73+$S$2*T72</f>
+        <f t="shared" si="5"/>
         <v>6.0042851227383922</v>
       </c>
       <c r="W73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.75013383839633041</v>
       </c>
     </row>
@@ -7275,15 +7364,15 @@
         <v>500</v>
       </c>
       <c r="R74" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2903225806451613</v>
       </c>
       <c r="T74" s="4">
-        <f>R74+$S$2*T73</f>
+        <f t="shared" si="5"/>
         <v>6.0937506788358755</v>
       </c>
       <c r="W74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.7528957736207833</v>
       </c>
     </row>
@@ -7292,15 +7381,15 @@
         <v>495</v>
       </c>
       <c r="R75" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2774193548387096</v>
       </c>
       <c r="T75" s="4">
-        <f>R75+$S$2*T74</f>
+        <f t="shared" si="5"/>
         <v>6.1524198979074107</v>
       </c>
       <c r="W75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.75467406916646107</v>
       </c>
     </row>
@@ -7309,15 +7398,15 @@
         <v>485</v>
       </c>
       <c r="R76" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.2516129032258065</v>
       </c>
       <c r="T76" s="4">
-        <f>R76+$S$2*T75</f>
+        <f t="shared" si="5"/>
         <v>6.1735488215517353</v>
       </c>
       <c r="W76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.75530824570026811</v>
       </c>
     </row>
@@ -7326,15 +7415,15 @@
         <v>505</v>
       </c>
       <c r="R77" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3032258064516129</v>
       </c>
       <c r="T77" s="4">
-        <f>R77+$S$2*T76</f>
+        <f t="shared" si="5"/>
         <v>6.2420648636930007</v>
       </c>
       <c r="W77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.75734236103744212</v>
       </c>
     </row>
@@ -7343,15 +7432,15 @@
         <v>510</v>
       </c>
       <c r="R78" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3161290322580645</v>
       </c>
       <c r="T78" s="4">
-        <f>R78+$S$2*T77</f>
+        <f t="shared" si="5"/>
         <v>6.3097809232124655</v>
       </c>
       <c r="W78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.75931976805631329</v>
       </c>
     </row>
@@ -7360,15 +7449,15 @@
         <v>520</v>
       </c>
       <c r="R79" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3419354838709678</v>
       </c>
       <c r="T79" s="4">
-        <f>R79+$S$2*T78</f>
+        <f t="shared" si="5"/>
         <v>6.3897602224409402</v>
       </c>
       <c r="W79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.76161416453233088</v>
       </c>
     </row>
@@ -7377,15 +7466,15 @@
         <v>515</v>
       </c>
       <c r="R80" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3290322580645162</v>
       </c>
       <c r="T80" s="4">
-        <f>R80+$S$2*T79</f>
+        <f t="shared" si="5"/>
         <v>6.4408404360172691</v>
       </c>
       <c r="W80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.7630567696237982</v>
       </c>
     </row>
@@ -7394,15 +7483,15 @@
         <v>530</v>
       </c>
       <c r="R81" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3677419354838709</v>
       </c>
       <c r="T81" s="4">
-        <f>R81+$S$2*T80</f>
+        <f t="shared" si="5"/>
         <v>6.5204142842976864</v>
       </c>
       <c r="W81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.76526962970734769</v>
       </c>
     </row>
@@ -7411,15 +7500,15 @@
         <v>540</v>
       </c>
       <c r="R82" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3935483870967742</v>
       </c>
       <c r="T82" s="4">
-        <f>R82+$S$2*T81</f>
+        <f t="shared" si="5"/>
         <v>6.6098798145349233</v>
       </c>
       <c r="W82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.76770872032108217</v>
       </c>
     </row>
@@ -7428,15 +7517,15 @@
         <v>535</v>
       </c>
       <c r="R83" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3806451612903226</v>
       </c>
       <c r="T83" s="4">
-        <f>R83+$S$2*T82</f>
+        <f t="shared" si="5"/>
         <v>6.6685490129182616</v>
       </c>
       <c r="W83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.76928087999277495</v>
       </c>
     </row>
@@ -7445,15 +7534,15 @@
         <v>525</v>
       </c>
       <c r="R84" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3548387096774193</v>
       </c>
       <c r="T84" s="4">
-        <f>R84+$S$2*T83</f>
+        <f t="shared" si="5"/>
         <v>6.6896779200120289</v>
       </c>
       <c r="W84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.76984187234442036</v>
       </c>
     </row>
@@ -7462,15 +7551,15 @@
         <v>545</v>
       </c>
       <c r="R85" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4064516129032258</v>
       </c>
       <c r="T85" s="4">
-        <f>R85+$S$2*T84</f>
+        <f t="shared" si="5"/>
         <v>6.7581939489128491</v>
       </c>
       <c r="W85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.77164241718485127</v>
       </c>
     </row>
@@ -7479,15 +7568,15 @@
         <v>550</v>
       </c>
       <c r="R86" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4193548387096775</v>
       </c>
       <c r="T86" s="4">
-        <f>R86+$S$2*T85</f>
+        <f t="shared" si="5"/>
         <v>6.8259099978399576</v>
       </c>
       <c r="W86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.77339447144946216</v>
       </c>
     </row>
@@ -7496,15 +7585,15 @@
         <v>560</v>
       </c>
       <c r="R87" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4451612903225806</v>
       </c>
       <c r="T87" s="4">
-        <f>R87+$S$2*T86</f>
+        <f t="shared" si="5"/>
         <v>6.9058892885945475</v>
       </c>
       <c r="W87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.77542950117723475</v>
       </c>
     </row>
@@ -7513,15 +7602,15 @@
         <v>555</v>
       </c>
       <c r="R88" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4322580645161291</v>
       </c>
       <c r="T88" s="4">
-        <f>R88+$S$2*T87</f>
+        <f t="shared" si="5"/>
         <v>6.9569694953917676</v>
       </c>
       <c r="W88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.77671019187583801</v>
       </c>
     </row>
@@ -7530,15 +7619,15 @@
         <v>570</v>
       </c>
       <c r="R89" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4709677419354839</v>
       </c>
       <c r="T89" s="4">
-        <f>R89+$S$2*T88</f>
+        <f t="shared" si="5"/>
         <v>7.0365433382488982</v>
       </c>
       <c r="W89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.77867643355013672</v>
       </c>
     </row>
@@ -7547,15 +7636,15 @@
         <v>580</v>
       </c>
       <c r="R90" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4967741935483871</v>
       </c>
       <c r="T90" s="4">
-        <f>R90+$S$2*T89</f>
+        <f t="shared" si="5"/>
         <v>7.1260088641475061</v>
       </c>
       <c r="W90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78084614755775528</v>
       </c>
     </row>
@@ -7564,15 +7653,15 @@
         <v>575</v>
       </c>
       <c r="R91" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4838709677419355</v>
       </c>
       <c r="T91" s="4">
-        <f>R91+$S$2*T90</f>
+        <f t="shared" si="5"/>
         <v>7.1846780590599408</v>
       </c>
       <c r="W91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78224604203441161</v>
       </c>
     </row>
@@ -7581,15 +7670,15 @@
         <v>565</v>
       </c>
       <c r="R92" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.4580645161290322</v>
       </c>
       <c r="T92" s="4">
-        <f>R92+$S$2*T91</f>
+        <f t="shared" si="5"/>
         <v>7.2058069633769852</v>
       </c>
       <c r="W92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.7827458246782163</v>
       </c>
     </row>
@@ -7598,15 +7687,15 @@
         <v>585</v>
       </c>
       <c r="R93" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5096774193548388</v>
       </c>
       <c r="T93" s="4">
-        <f>R93+$S$2*T92</f>
+        <f t="shared" si="5"/>
         <v>7.2743229900564277</v>
       </c>
       <c r="W93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78435083594303079</v>
       </c>
     </row>
@@ -7615,15 +7704,15 @@
         <v>590</v>
       </c>
       <c r="R94" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5225806451612902</v>
       </c>
       <c r="T94" s="4">
-        <f>R94+$S$2*T93</f>
+        <f t="shared" si="5"/>
         <v>7.3420390372064324</v>
       </c>
       <c r="W94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78591397530725104</v>
       </c>
     </row>
@@ -7632,15 +7721,15 @@
         <v>600</v>
       </c>
       <c r="R95" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5483870967741935</v>
       </c>
       <c r="T95" s="4">
-        <f>R95+$S$2*T94</f>
+        <f t="shared" si="5"/>
         <v>7.4220183265393391</v>
       </c>
       <c r="W95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78773125558814427</v>
       </c>
     </row>
@@ -7649,15 +7738,15 @@
         <v>595</v>
       </c>
       <c r="R96" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5354838709677419</v>
       </c>
       <c r="T96" s="4">
-        <f>R96+$S$2*T95</f>
+        <f t="shared" si="5"/>
         <v>7.4730985321992129</v>
       </c>
       <c r="W96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78887583685507245</v>
       </c>
     </row>
@@ -7666,15 +7755,15 @@
         <v>610</v>
       </c>
       <c r="R97" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5741935483870968</v>
       </c>
       <c r="T97" s="4">
-        <f>R97+$S$2*T96</f>
+        <f t="shared" si="5"/>
         <v>7.5526723741464679</v>
       </c>
       <c r="W97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79063450292581605</v>
       </c>
     </row>
@@ -7683,15 +7772,15 @@
         <v>620</v>
       </c>
       <c r="R98" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="T98" s="4">
-        <f>R98+$S$2*T97</f>
+        <f t="shared" si="5"/>
         <v>7.6421378993171754</v>
       </c>
       <c r="W98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79257712128949809</v>
       </c>
     </row>
@@ -7700,15 +7789,15 @@
         <v>615</v>
       </c>
       <c r="R99" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5870967741935484</v>
       </c>
       <c r="T99" s="4">
-        <f>R99+$S$2*T98</f>
+        <f t="shared" ref="T99:T105" si="7">R99+$S$2*T98</f>
         <v>7.7008070936472892</v>
       </c>
       <c r="W99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79383158734186898</v>
       </c>
     </row>
@@ -7717,15 +7806,15 @@
         <v>605</v>
       </c>
       <c r="R100" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.5612903225806452</v>
       </c>
       <c r="T100" s="4">
-        <f>R100+$S$2*T99</f>
+        <f t="shared" si="7"/>
         <v>7.7219359974984769</v>
       </c>
       <c r="W100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79427965782590892</v>
       </c>
     </row>
@@ -7734,15 +7823,15 @@
         <v>625</v>
       </c>
       <c r="R101" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6129032258064515</v>
       </c>
       <c r="T101" s="4">
-        <f>R101+$S$2*T100</f>
+        <f t="shared" si="7"/>
         <v>7.7904520238052335</v>
       </c>
       <c r="W101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79571934011452672</v>
       </c>
     </row>
@@ -7751,15 +7840,15 @@
         <v>630</v>
       </c>
       <c r="R102" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6258064516129032</v>
       </c>
       <c r="T102" s="4">
-        <f>R102+$S$2*T101</f>
+        <f t="shared" si="7"/>
         <v>7.8581680706570909</v>
       </c>
       <c r="W102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79712254998441201</v>
       </c>
     </row>
@@ -7768,15 +7857,15 @@
         <v>640</v>
       </c>
       <c r="R103" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6516129032258065</v>
       </c>
       <c r="T103" s="4">
-        <f>R103+$S$2*T102</f>
+        <f t="shared" si="7"/>
         <v>7.9381473597514791</v>
       </c>
       <c r="W103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.7987552480757325</v>
       </c>
     </row>
@@ -7785,15 +7874,15 @@
         <v>635</v>
       </c>
       <c r="R104" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6387096774193548</v>
       </c>
       <c r="T104" s="4">
-        <f>R104+$S$2*T103</f>
+        <f t="shared" si="7"/>
         <v>7.9892275652205385</v>
       </c>
       <c r="W104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79978431896342084</v>
       </c>
     </row>
@@ -7802,15 +7891,15 @@
         <v>650</v>
       </c>
       <c r="R105" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6774193548387097</v>
       </c>
       <c r="T105" s="4">
-        <f>R105+$S$2*T104</f>
+        <f t="shared" si="7"/>
         <v>8.0688014070151404</v>
       </c>
       <c r="W105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.80136662556413529</v>
       </c>
     </row>
@@ -7822,30 +7911,208 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA2D22E4-72C8-48EC-B272-C0FE7D7AA382}">
-  <dimension ref="B3:D7"/>
+  <dimension ref="B3:W30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="15" max="15" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>0</v>
       </c>
       <c r="D3">
         <v>500</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>505</v>
+      </c>
+      <c r="N5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>20000</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>30000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="H10" t="s">
+        <v>510</v>
+      </c>
+      <c r="I10" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="H11" t="s">
+        <v>512</v>
+      </c>
+      <c r="I11" t="s">
+        <v>514</v>
+      </c>
+      <c r="K11">
+        <f>100/200</f>
+        <v>0.5</v>
+      </c>
+      <c r="L11">
+        <f>2/3</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O11" t="s">
+        <v>518</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>508</v>
+      </c>
+      <c r="E12" t="s">
+        <v>509</v>
+      </c>
+      <c r="H12" t="s">
+        <v>513</v>
+      </c>
+      <c r="I12" t="s">
+        <v>515</v>
+      </c>
+      <c r="K12">
+        <f>200/200</f>
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <f>3/3</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="H13" t="s">
+        <v>516</v>
+      </c>
+      <c r="I13" t="s">
+        <v>517</v>
+      </c>
+      <c r="K13">
+        <f>300/200</f>
+        <v>1.5</v>
+      </c>
+      <c r="L13">
+        <f>4/3</f>
+        <v>1.3333333333333333</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="Q16" t="s">
+        <v>525</v>
+      </c>
+      <c r="S16" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="18" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>519</v>
+      </c>
+      <c r="L18" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="19" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="H19" t="s">
+        <v>520</v>
+      </c>
+      <c r="L19" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="22" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="V22" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="W22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="23" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="N23" t="s">
+        <v>510</v>
+      </c>
+      <c r="O23" t="s">
+        <v>511</v>
+      </c>
+      <c r="P23" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>529</v>
+      </c>
+      <c r="V23">
+        <v>50</v>
+      </c>
+      <c r="W23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="V24">
+        <v>60</v>
+      </c>
+      <c r="W24">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="V25">
+        <v>30</v>
+      </c>
+      <c r="W25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="G26" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="27" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="G27" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="30" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="O30" t="s">
+        <v>531</v>
+      </c>
+      <c r="P30" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/mmm_104_weeks_dataset.xlsx
+++ b/mmm_104_weeks_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\MMM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FE29FC-AD74-4F9C-A1D9-FA605BD20D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{094FBFC2-AC66-45D4-8EE6-28FBC8BA8282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
